--- a/документы/Опросный-лист-сырьё.xlsx
+++ b/документы/Опросный-лист-сырьё.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1387,41 +1387,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Есть на складе</t>
-        </is>
-      </c>
-      <c r="C32" s="9">
-        <f>COUNTIF(E8:E29,"Есть на складе")</f>
-        <v/>
-      </c>
-    </row>
     <row r="33">
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="C33" s="9">
-        <f>COUNTIF(E8:E29,"Под заказ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="C34" s="9">
-        <f>COUNTIF(E8:E29,"Нет")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>ИП Мясоедов Алексей Владимирович · +375 33 628-04-86 · miasoedov95@gmail.com</t>
         </is>
@@ -1449,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2080,41 +2047,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Есть на складе</t>
-        </is>
-      </c>
-      <c r="C24" s="9">
-        <f>COUNTIF(E8:E21,"Есть на складе")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25">
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Под заказ</t>
-        </is>
-      </c>
-      <c r="C25" s="9">
-        <f>COUNTIF(E8:E21,"Под заказ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="C26" s="9">
-        <f>COUNTIF(E8:E21,"Нет")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ИП Мясоедов Алексей Владимирович · +375 33 628-04-86 · miasoedov95@gmail.com</t>
         </is>
